--- a/branches/dependabot/github_actions/dev/actions-d025328a43/CodeSystem-mii-cs-seltene-hpo-change-status.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-d025328a43/CodeSystem-mii-cs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T01:49:31+00:00</t>
+    <t>2026-09-14T01:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
